--- a/report-saved-customers-summary.xlsx
+++ b/report-saved-customers-summary.xlsx
@@ -11,15 +11,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
   <si>
     <t>Customer Report</t>
   </si>
   <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Skyinventories</t>
+  </si>
+  <si>
     <t>Generated At</t>
   </si>
   <si>
-    <t>02 Apr 2026, 09:11</t>
+    <t>02 Apr 2026, 09:24</t>
   </si>
   <si>
     <t>Mode</t>
@@ -515,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -560,64 +566,72 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25"/>
-    <row r="7" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="5"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B6" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="5"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25"/>
-    <row r="10" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="5"/>
-    </row>
-    <row r="11" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="8" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="B11" s="5"/>
+    </row>
+    <row r="12" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:2" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="5"/>
+    </row>
+    <row r="16" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="5"/>
-    </row>
-    <row r="15" spans="1:2" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" s="4">
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="4">
         <v>2</v>
       </c>
     </row>
